--- a/01_Project_Documentation/phase1/P1_07_Data_Dictionary.xlsx
+++ b/01_Project_Documentation/phase1/P1_07_Data_Dictionary.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -609,105 +609,117 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>[Team member names - Student IDs]</t>
+          <t>Kashish Fatima (24L-2605); Khadija Faiz (24L-2554); Aliyah Rasheed (24L-2544)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Section / instructor</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>BDS5A / Esha Tur Razia Babar</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Key role legend</t>
-        </is>
-      </c>
+      <c r="A11" s="3" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Primary key of the warehouse table</t>
-        </is>
-      </c>
+          <t>Key role legend</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>NK</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Natural (business) key from the source system; unique in the dimension</t>
+          <t>Primary key of the warehouse table</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>NK</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Foreign key to a dimension surrogate key</t>
+          <t>Natural (business) key from the source system; unique in the dimension</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>FK</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Degenerate dimension (identifier/attribute kept in the fact without its own dimension)</t>
+          <t>Foreign key to a dimension surrogate key</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Measure (numeric fact); see 'Additivity' column</t>
+          <t>Degenerate dimension (identifier/attribute kept in the fact without its own dimension)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Measure (numeric fact); see 'Additivity' column</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Descriptive attribute</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Sheets</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Tables, Columns, Relationships, Bus_Matrix, Hierarchies, Measures, Lookup_Values, Business_Questions, Transformation_Rules, Source_Profile</t>
         </is>
@@ -7342,7 +7354,7 @@
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>delivered::date - estimated::date; NULL if not delivered</t>
+          <t>delivered::date - estimated::date when is_delivered = 1; otherwise NULL</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
@@ -7452,7 +7464,7 @@
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>1 if delivered after the estimated date, 0 if on time; NULL if not delivered.</t>
+          <t>1 if delivered after the estimated date, 0 if on time; NULL when is_delivered = 0.</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
@@ -7462,7 +7474,7 @@
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>delivery_delay_days &gt; 0</t>
+          <t>CASE WHEN is_delivered = 1 THEN (delivery_delay_days &gt; 0)::int END</t>
         </is>
       </c>
       <c r="K89" s="6" t="inlineStr">
